--- a/src/test/resources/testData/UserData.xlsx
+++ b/src/test/resources/testData/UserData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="422">
   <si>
     <t>Job title</t>
   </si>
@@ -1273,6 +1273,57 @@
   </si>
   <si>
     <t>virat_1790687981739</t>
+  </si>
+  <si>
+    <t>ESS Test user1</t>
+  </si>
+  <si>
+    <t>Tomo Testas</t>
+  </si>
+  <si>
+    <t>qa.qn2dbf</t>
+  </si>
+  <si>
+    <t>Kyla Keebler</t>
+  </si>
+  <si>
+    <t>ess.0eesmj</t>
+  </si>
+  <si>
+    <t>WilfredAZGM3 Streich-DeckowAZGM3</t>
+  </si>
+  <si>
+    <t>ess.g5rec2</t>
+  </si>
+  <si>
+    <t>RubyXEFZW BlandaXEFZW</t>
+  </si>
+  <si>
+    <t>qa.c3qnok</t>
+  </si>
+  <si>
+    <t>Adolf Bode</t>
+  </si>
+  <si>
+    <t>DEMO123</t>
+  </si>
+  <si>
+    <t>e2e_admin_1790756953996122</t>
+  </si>
+  <si>
+    <t>e2e_admin_1790757114397717</t>
+  </si>
+  <si>
+    <t>e2e_admin_1790757455092827</t>
+  </si>
+  <si>
+    <t>User_James.Smith_56467267</t>
+  </si>
+  <si>
+    <t>User_James.Smith_56579547</t>
+  </si>
+  <si>
+    <t>User_James.Smith_56742365</t>
   </si>
 </sst>
 </file>
@@ -1603,7 +1654,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>369</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>8</v>
@@ -1614,13 +1665,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>8</v>
@@ -1631,13 +1682,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>371</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>8</v>
@@ -1648,13 +1699,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>373</v>
+        <v>417</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>6</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>262</v>
+        <v>197</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>8</v>
@@ -1665,13 +1716,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>374</v>
+        <v>418</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>375</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>8</v>
@@ -1682,13 +1733,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>13</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>8</v>
@@ -1699,13 +1750,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>26</v>
+        <v>409</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>13</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>27</v>
+        <v>410</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>8</v>
@@ -1716,13 +1767,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>28</v>
+        <v>411</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>29</v>
+        <v>412</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>8</v>
@@ -1733,13 +1784,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>33</v>
+        <v>399</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>8</v>
@@ -1750,13 +1801,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>378</v>
+        <v>413</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>237</v>
+        <v>414</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>8</v>
@@ -1767,13 +1818,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>13</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>237</v>
+        <v>408</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>8</v>
@@ -1784,13 +1835,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>13</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>237</v>
+        <v>399</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>8</v>
@@ -1801,13 +1852,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>381</v>
+        <v>420</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>13</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>8</v>
@@ -1818,13 +1869,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>383</v>
+        <v>421</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>37</v>
+        <v>399</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>8</v>
